--- a/Labs_and_others/Data_Analytics/Final_Exam_Assignment/solutions/sales_analysis.xlsx
+++ b/Labs_and_others/Data_Analytics/Final_Exam_Assignment/solutions/sales_analysis.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
-  <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tanak\Desktop\AIT-2024\Labs and others\Data Analytics\Final_Exam_Assignment\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tanak\Desktop\AIT-2024\Labs_and_others\Data_Analytics\Final_Exam_Assignment\solutions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{6EA57095-314F-4434-90DB-96481CB59B71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5594A3DD-2E25-451F-8B62-78D520A1EFD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="24792" windowHeight="15576" xr2:uid="{4D012305-7D00-4A69-8AC6-356F828A0284}"/>
   </bookViews>
@@ -18,10 +18,23 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sales_data!$A$1:$H$32</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="17" r:id="rId2"/>
+    <pivotCache cacheId="1" r:id="rId2"/>
   </pivotCaches>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -668,7 +681,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
@@ -676,7 +689,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -805,7 +817,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="ru-RU"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -1228,7 +1240,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="ru-RU"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -3207,7 +3219,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{496CCD33-7DB7-4302-8CAD-791461CD7F98}" name="PivotTable5" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="15">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{496CCD33-7DB7-4302-8CAD-791461CD7F98}" name="PivotTable5" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="17">
   <location ref="T1:U5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0"/>
@@ -3296,7 +3308,7 @@
   <dataFields count="1">
     <dataField name="Sum of revenue" fld="8" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="2">
+  <chartFormats count="3">
     <chartFormat chart="7" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -3307,6 +3319,15 @@
       </pivotArea>
     </chartFormat>
     <chartFormat chart="14" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="16" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -3329,7 +3350,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{38AC0465-4C02-425D-A42B-D9E4BBBF000A}" name="PivotTable4" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{38AC0465-4C02-425D-A42B-D9E4BBBF000A}" name="PivotTable4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="P1:Q6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0"/>
@@ -3442,7 +3463,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E4BDAFC4-62A8-4AA3-B437-D88D8FAC6D9B}" name="PivotTable3" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E4BDAFC4-62A8-4AA3-B437-D88D8FAC6D9B}" name="PivotTable3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
   <location ref="L1:M5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0"/>
@@ -3905,6 +3926,8 @@
     <col min="17" max="17" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.3">
@@ -3987,19 +4010,19 @@
       <c r="L2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M2" s="5">
+      <c r="M2">
         <v>6610</v>
       </c>
       <c r="P2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="Q2" s="5">
+      <c r="Q2">
         <v>1921</v>
       </c>
       <c r="T2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="U2" s="5">
+      <c r="U2">
         <v>2666</v>
       </c>
     </row>
@@ -4035,19 +4058,19 @@
       <c r="L3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M3" s="5">
+      <c r="M3">
         <v>1970</v>
       </c>
       <c r="P3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="Q3" s="5">
+      <c r="Q3">
         <v>3775</v>
       </c>
       <c r="T3" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="U3" s="5">
+      <c r="U3">
         <v>3760</v>
       </c>
     </row>
@@ -4083,19 +4106,19 @@
       <c r="L4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="M4" s="5">
+      <c r="M4">
         <v>369</v>
       </c>
       <c r="P4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="Q4" s="5">
+      <c r="Q4">
         <v>2263</v>
       </c>
       <c r="T4" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="U4" s="5">
+      <c r="U4">
         <v>2523</v>
       </c>
     </row>
@@ -4131,19 +4154,19 @@
       <c r="L5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="M5" s="5">
+      <c r="M5">
         <v>8949</v>
       </c>
       <c r="P5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="Q5" s="5">
+      <c r="Q5">
         <v>990</v>
       </c>
       <c r="T5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="U5" s="5">
+      <c r="U5">
         <v>8949</v>
       </c>
     </row>
@@ -4179,7 +4202,7 @@
       <c r="P6" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="Q6" s="5">
+      <c r="Q6">
         <v>8949</v>
       </c>
     </row>

--- a/Labs_and_others/Data_Analytics/Final_Exam_Assignment/solutions/sales_analysis.xlsx
+++ b/Labs_and_others/Data_Analytics/Final_Exam_Assignment/solutions/sales_analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tanak\Desktop\AIT-2024\Labs_and_others\Data_Analytics\Final_Exam_Assignment\solutions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5594A3DD-2E25-451F-8B62-78D520A1EFD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37BFDB5D-1A06-46D8-886C-8B7EC5DB3D80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="24792" windowHeight="15576" xr2:uid="{4D012305-7D00-4A69-8AC6-356F828A0284}"/>
   </bookViews>
@@ -20,7 +20,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId2"/>
+    <pivotCache cacheId="2" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -2815,7 +2815,18 @@
       <fieldGroup par="9"/>
     </cacheField>
     <cacheField name="customer_id" numFmtId="0">
-      <sharedItems/>
+      <sharedItems count="10">
+        <s v="C001"/>
+        <s v="C002"/>
+        <s v="C003"/>
+        <s v="C004"/>
+        <s v="C005"/>
+        <s v="C006"/>
+        <s v="C007"/>
+        <s v="C008"/>
+        <s v="C009"/>
+        <s v="C010"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="product" numFmtId="0">
       <sharedItems/>
@@ -2888,7 +2899,7 @@
   <r>
     <n v="1001"/>
     <x v="0"/>
-    <s v="C001"/>
+    <x v="0"/>
     <s v="Laptop Pro"/>
     <x v="0"/>
     <n v="1200"/>
@@ -2899,7 +2910,7 @@
   <r>
     <n v="1002"/>
     <x v="1"/>
-    <s v="C002"/>
+    <x v="1"/>
     <s v="Wireless Mouse"/>
     <x v="0"/>
     <n v="25"/>
@@ -2910,7 +2921,7 @@
   <r>
     <n v="1003"/>
     <x v="2"/>
-    <s v="C003"/>
+    <x v="2"/>
     <s v="Office Chair"/>
     <x v="1"/>
     <n v="180"/>
@@ -2921,7 +2932,7 @@
   <r>
     <n v="1004"/>
     <x v="3"/>
-    <s v="C001"/>
+    <x v="0"/>
     <s v="USB-C Hub"/>
     <x v="0"/>
     <n v="45"/>
@@ -2932,7 +2943,7 @@
   <r>
     <n v="1005"/>
     <x v="4"/>
-    <s v="C004"/>
+    <x v="3"/>
     <s v="Standing Desk"/>
     <x v="1"/>
     <n v="350"/>
@@ -2943,7 +2954,7 @@
   <r>
     <n v="1006"/>
     <x v="5"/>
-    <s v="C005"/>
+    <x v="4"/>
     <s v="Notebook"/>
     <x v="2"/>
     <n v="5"/>
@@ -2954,7 +2965,7 @@
   <r>
     <n v="1007"/>
     <x v="6"/>
-    <s v="C006"/>
+    <x v="5"/>
     <s v="Pen Set"/>
     <x v="2"/>
     <n v="12"/>
@@ -2965,7 +2976,7 @@
   <r>
     <n v="1008"/>
     <x v="7"/>
-    <s v="C002"/>
+    <x v="1"/>
     <s v="Keyboard"/>
     <x v="0"/>
     <n v="75"/>
@@ -2976,7 +2987,7 @@
   <r>
     <n v="1009"/>
     <x v="8"/>
-    <s v="C007"/>
+    <x v="6"/>
     <s v="Monitor 27&quot;"/>
     <x v="0"/>
     <n v="300"/>
@@ -2987,7 +2998,7 @@
   <r>
     <n v="1010"/>
     <x v="9"/>
-    <s v="C008"/>
+    <x v="7"/>
     <s v="Desk Lamp"/>
     <x v="1"/>
     <n v="40"/>
@@ -2998,7 +3009,7 @@
   <r>
     <n v="1011"/>
     <x v="10"/>
-    <s v="C001"/>
+    <x v="0"/>
     <s v="Laptop Pro"/>
     <x v="0"/>
     <n v="1200"/>
@@ -3009,7 +3020,7 @@
   <r>
     <n v="1012"/>
     <x v="11"/>
-    <s v="C009"/>
+    <x v="8"/>
     <s v="Office Chair"/>
     <x v="1"/>
     <n v="180"/>
@@ -3020,7 +3031,7 @@
   <r>
     <n v="1013"/>
     <x v="12"/>
-    <s v="C010"/>
+    <x v="9"/>
     <s v="Notebook"/>
     <x v="2"/>
     <n v="5"/>
@@ -3031,7 +3042,7 @@
   <r>
     <n v="1014"/>
     <x v="13"/>
-    <s v="C003"/>
+    <x v="2"/>
     <s v="Keyboard"/>
     <x v="0"/>
     <n v="75"/>
@@ -3042,7 +3053,7 @@
   <r>
     <n v="1015"/>
     <x v="14"/>
-    <s v="C004"/>
+    <x v="3"/>
     <s v="Monitor 27&quot;"/>
     <x v="0"/>
     <n v="300"/>
@@ -3053,7 +3064,7 @@
   <r>
     <n v="1016"/>
     <x v="15"/>
-    <s v="C005"/>
+    <x v="4"/>
     <s v="Desk Lamp"/>
     <x v="1"/>
     <n v="40"/>
@@ -3064,7 +3075,7 @@
   <r>
     <n v="1017"/>
     <x v="16"/>
-    <s v="C006"/>
+    <x v="5"/>
     <s v="Wireless Mouse"/>
     <x v="0"/>
     <n v="25"/>
@@ -3075,7 +3086,7 @@
   <r>
     <n v="1018"/>
     <x v="17"/>
-    <s v="C007"/>
+    <x v="6"/>
     <s v="Standing Desk"/>
     <x v="1"/>
     <n v="350"/>
@@ -3086,7 +3097,7 @@
   <r>
     <n v="1019"/>
     <x v="18"/>
-    <s v="C008"/>
+    <x v="7"/>
     <s v="Pen Set"/>
     <x v="2"/>
     <n v="12"/>
@@ -3097,7 +3108,7 @@
   <r>
     <n v="1020"/>
     <x v="19"/>
-    <s v="C002"/>
+    <x v="1"/>
     <s v="Laptop Pro"/>
     <x v="0"/>
     <n v="1200"/>
@@ -3108,7 +3119,7 @@
   <r>
     <n v="1021"/>
     <x v="20"/>
-    <s v="C009"/>
+    <x v="8"/>
     <s v="USB-C Hub"/>
     <x v="0"/>
     <n v="45"/>
@@ -3119,7 +3130,7 @@
   <r>
     <n v="1022"/>
     <x v="21"/>
-    <s v="C010"/>
+    <x v="9"/>
     <s v="Office Chair"/>
     <x v="1"/>
     <n v="180"/>
@@ -3130,7 +3141,7 @@
   <r>
     <n v="1023"/>
     <x v="22"/>
-    <s v="C001"/>
+    <x v="0"/>
     <s v="Monitor 27&quot;"/>
     <x v="0"/>
     <n v="300"/>
@@ -3141,7 +3152,7 @@
   <r>
     <n v="1024"/>
     <x v="23"/>
-    <s v="C003"/>
+    <x v="2"/>
     <s v="Notebook"/>
     <x v="2"/>
     <n v="5"/>
@@ -3152,7 +3163,7 @@
   <r>
     <n v="1025"/>
     <x v="24"/>
-    <s v="C004"/>
+    <x v="3"/>
     <s v="Keyboard"/>
     <x v="0"/>
     <n v="75"/>
@@ -3163,7 +3174,7 @@
   <r>
     <n v="1026"/>
     <x v="25"/>
-    <s v="C005"/>
+    <x v="4"/>
     <s v="Standing Desk"/>
     <x v="1"/>
     <n v="350"/>
@@ -3174,7 +3185,7 @@
   <r>
     <n v="1027"/>
     <x v="26"/>
-    <s v="C006"/>
+    <x v="5"/>
     <s v="Laptop Pro"/>
     <x v="0"/>
     <n v="1200"/>
@@ -3185,7 +3196,7 @@
   <r>
     <n v="1028"/>
     <x v="27"/>
-    <s v="C007"/>
+    <x v="6"/>
     <s v="Desk Lamp"/>
     <x v="1"/>
     <n v="40"/>
@@ -3196,7 +3207,7 @@
   <r>
     <n v="1029"/>
     <x v="28"/>
-    <s v="C008"/>
+    <x v="7"/>
     <s v="Wireless Mouse"/>
     <x v="0"/>
     <n v="25"/>
@@ -3207,7 +3218,7 @@
   <r>
     <n v="1030"/>
     <x v="29"/>
-    <s v="C009"/>
+    <x v="8"/>
     <s v="Pen Set"/>
     <x v="2"/>
     <n v="12"/>
@@ -3219,7 +3230,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{496CCD33-7DB7-4302-8CAD-791461CD7F98}" name="PivotTable5" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="17">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{496CCD33-7DB7-4302-8CAD-791461CD7F98}" name="PivotTable5" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="17">
   <location ref="T1:U5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0"/>
@@ -3350,7 +3361,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{38AC0465-4C02-425D-A42B-D9E4BBBF000A}" name="PivotTable4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{38AC0465-4C02-425D-A42B-D9E4BBBF000A}" name="PivotTable4" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="P1:Q6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0"/>
@@ -3463,7 +3474,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E4BDAFC4-62A8-4AA3-B437-D88D8FAC6D9B}" name="PivotTable3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E4BDAFC4-62A8-4AA3-B437-D88D8FAC6D9B}" name="PivotTable3" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
   <location ref="L1:M5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0"/>
@@ -3926,8 +3937,8 @@
     <col min="17" max="17" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="12.44140625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.3">
